--- a/results/PC/shp_opt/PC_shp_opt_events.xlsx
+++ b/results/PC/shp_opt/PC_shp_opt_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="57">
   <si>
     <t>date_p1</t>
   </si>
@@ -43,10 +43,16 @@
     <t>N0</t>
   </si>
   <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
     <t>2025-06-01</t>
   </si>
   <si>
-    <t>2025-06-02</t>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>2025-06-07</t>
   </si>
   <si>
     <t>2025-06-29</t>
@@ -61,24 +67,78 @@
     <t>2025-07-02</t>
   </si>
   <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>2025-07-04</t>
+  </si>
+  <si>
+    <t>2025-07-05</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>2025-07-07</t>
+  </si>
+  <si>
     <t>2025-07-23</t>
   </si>
   <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>2025-10-20</t>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>2025-07-25</t>
+  </si>
+  <si>
+    <t>2025-07-26</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>2025-08-17</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>2025-08-20</t>
   </si>
   <si>
     <t>2025-10-21</t>
   </si>
   <si>
-    <t>2025-06-11</t>
+    <t>2025-10-22</t>
+  </si>
+  <si>
+    <t>2025-10-24</t>
+  </si>
+  <si>
+    <t>2025-10-26</t>
+  </si>
+  <si>
+    <t>2025-04-30</t>
+  </si>
+  <si>
+    <t>2025-06-06</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
   </si>
   <si>
     <t>2025-06-12</t>
   </si>
   <si>
+    <t>2025-07-08</t>
+  </si>
+  <si>
     <t>2025-07-09</t>
   </si>
   <si>
@@ -91,13 +151,37 @@
     <t>2025-07-12</t>
   </si>
   <si>
+    <t>2025-07-29</t>
+  </si>
+  <si>
+    <t>2025-07-30</t>
+  </si>
+  <si>
+    <t>2025-07-31</t>
+  </si>
+  <si>
+    <t>2025-08-01</t>
+  </si>
+  <si>
     <t>2025-08-02</t>
   </si>
   <si>
+    <t>2025-08-22</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>2025-08-24</t>
+  </si>
+  <si>
+    <t>2025-08-25</t>
+  </si>
+  <si>
+    <t>2025-10-27</t>
+  </si>
+  <si>
     <t>2025-10-29</t>
-  </si>
-  <si>
-    <t>2025-10-30</t>
   </si>
   <si>
     <t>2025-10-31</t>
@@ -458,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -495,28 +579,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C2">
-        <v>0.27189</v>
+        <v>0.32458</v>
       </c>
       <c r="D2">
-        <v>1480.43</v>
+        <v>1392.18</v>
       </c>
       <c r="E2">
-        <v>0.1845</v>
+        <v>0.29253</v>
       </c>
       <c r="F2">
-        <v>1539.85</v>
+        <v>1436.63</v>
       </c>
       <c r="G2">
-        <v>0.08739</v>
+        <v>0.03204</v>
       </c>
       <c r="H2">
-        <v>0.367572</v>
+        <v>0.06608600000000001</v>
       </c>
       <c r="I2">
-        <v>2970.623</v>
+        <v>2405.175</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -524,28 +608,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C3">
-        <v>0.26259</v>
+        <v>0.27189</v>
       </c>
       <c r="D3">
-        <v>1511.27</v>
+        <v>1480.43</v>
       </c>
       <c r="E3">
-        <v>0.17832</v>
+        <v>0.22012</v>
       </c>
       <c r="F3">
-        <v>1557.85</v>
+        <v>1527.94</v>
       </c>
       <c r="G3">
-        <v>0.08427</v>
+        <v>0.05177</v>
       </c>
       <c r="H3">
-        <v>0.456121</v>
+        <v>0.252394</v>
       </c>
       <c r="I3">
-        <v>3119.72</v>
+        <v>2813.887</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -553,28 +637,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="C4">
-        <v>0.32839</v>
+        <v>0.24499</v>
       </c>
       <c r="D4">
-        <v>1376.51</v>
+        <v>1490.27</v>
       </c>
       <c r="E4">
-        <v>0.24946</v>
+        <v>0.19656</v>
       </c>
       <c r="F4">
-        <v>1478.33</v>
+        <v>1531.98</v>
       </c>
       <c r="G4">
-        <v>0.07893</v>
+        <v>0.04842</v>
       </c>
       <c r="H4">
-        <v>0.106155</v>
+        <v>0.297902</v>
       </c>
       <c r="I4">
-        <v>2467.117</v>
+        <v>2861.319</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -582,28 +666,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C5">
-        <v>0.31332</v>
+        <v>0.20974</v>
       </c>
       <c r="D5">
-        <v>1393.44</v>
+        <v>1513.31</v>
       </c>
       <c r="E5">
-        <v>0.23436</v>
+        <v>0.17832</v>
       </c>
       <c r="F5">
-        <v>1509.83</v>
+        <v>1557.85</v>
       </c>
       <c r="G5">
-        <v>0.07895000000000001</v>
+        <v>0.03141</v>
       </c>
       <c r="H5">
-        <v>0.094239</v>
+        <v>0.194634</v>
       </c>
       <c r="I5">
-        <v>2443.537</v>
+        <v>2646.489</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -611,28 +695,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C6">
-        <v>0.30572</v>
+        <v>0.32839</v>
       </c>
       <c r="D6">
-        <v>1407.38</v>
+        <v>1376.51</v>
       </c>
       <c r="E6">
-        <v>0.21968</v>
+        <v>0.2886</v>
       </c>
       <c r="F6">
-        <v>1519.8</v>
+        <v>1422.24</v>
       </c>
       <c r="G6">
-        <v>0.08604000000000001</v>
+        <v>0.03979</v>
       </c>
       <c r="H6">
-        <v>0.135611</v>
+        <v>0.108888</v>
       </c>
       <c r="I6">
-        <v>2535.455</v>
+        <v>2472.268</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -640,28 +724,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>0.29992</v>
+        <v>0.31332</v>
       </c>
       <c r="D7">
-        <v>1408.23</v>
+        <v>1393.44</v>
       </c>
       <c r="E7">
-        <v>0.208</v>
+        <v>0.28379</v>
       </c>
       <c r="F7">
-        <v>1556.6</v>
+        <v>1416.02</v>
       </c>
       <c r="G7">
-        <v>0.09192</v>
+        <v>0.02952</v>
       </c>
       <c r="H7">
-        <v>0.099373</v>
+        <v>0.233905</v>
       </c>
       <c r="I7">
-        <v>2451.822</v>
+        <v>2681.471</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -669,28 +753,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C8">
-        <v>0.32379</v>
+        <v>0.30572</v>
       </c>
       <c r="D8">
-        <v>1378.5</v>
+        <v>1407.38</v>
       </c>
       <c r="E8">
-        <v>0.20527</v>
+        <v>0.27907</v>
       </c>
       <c r="F8">
-        <v>1523.66</v>
+        <v>1430.22</v>
       </c>
       <c r="G8">
-        <v>0.11852</v>
+        <v>0.02665</v>
       </c>
       <c r="H8">
-        <v>0.149031</v>
+        <v>0.208686</v>
       </c>
       <c r="I8">
-        <v>2539.201</v>
+        <v>2660.091</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -698,28 +782,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C9">
-        <v>0.3529</v>
+        <v>0.29992</v>
       </c>
       <c r="D9">
-        <v>1359.55</v>
+        <v>1408.23</v>
       </c>
       <c r="E9">
-        <v>0.30698</v>
+        <v>0.27285</v>
       </c>
       <c r="F9">
-        <v>1431.45</v>
+        <v>1442.77</v>
       </c>
       <c r="G9">
-        <v>0.04592</v>
+        <v>0.02707</v>
       </c>
       <c r="H9">
-        <v>0.01523</v>
+        <v>0.109563</v>
       </c>
       <c r="I9">
-        <v>2298.523</v>
+        <v>2473.51</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -727,28 +811,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C10">
-        <v>0.34092</v>
+        <v>0.29428</v>
       </c>
       <c r="D10">
-        <v>1373.75</v>
+        <v>1410.69</v>
       </c>
       <c r="E10">
-        <v>0.30514</v>
+        <v>0.26155</v>
       </c>
       <c r="F10">
-        <v>1429.66</v>
+        <v>1456.52</v>
       </c>
       <c r="G10">
-        <v>0.03578</v>
+        <v>0.03273</v>
       </c>
       <c r="H10">
-        <v>0.023332</v>
+        <v>0.097662</v>
       </c>
       <c r="I10">
-        <v>2313.41</v>
+        <v>2440.002</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -756,28 +840,521 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11">
+        <v>0.2886</v>
+      </c>
+      <c r="D11">
+        <v>1422.24</v>
+      </c>
+      <c r="E11">
+        <v>0.24946</v>
+      </c>
+      <c r="F11">
+        <v>1478.33</v>
+      </c>
+      <c r="G11">
+        <v>0.03914</v>
+      </c>
+      <c r="H11">
+        <v>0.104025</v>
+      </c>
+      <c r="I11">
+        <v>2461.495</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12">
+        <v>0.28379</v>
+      </c>
+      <c r="D12">
+        <v>1416.02</v>
+      </c>
+      <c r="E12">
+        <v>0.23436</v>
+      </c>
+      <c r="F12">
+        <v>1509.83</v>
+      </c>
+      <c r="G12">
+        <v>0.04943</v>
+      </c>
+      <c r="H12">
+        <v>0.056374</v>
+      </c>
+      <c r="I12">
+        <v>2323.134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13">
+        <v>0.27907</v>
+      </c>
+      <c r="D13">
+        <v>1430.22</v>
+      </c>
+      <c r="E13">
+        <v>0.21968</v>
+      </c>
+      <c r="F13">
+        <v>1519.8</v>
+      </c>
+      <c r="G13">
+        <v>0.05939</v>
+      </c>
+      <c r="H13">
+        <v>0.116438</v>
+      </c>
+      <c r="I13">
+        <v>2481.743</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14">
+        <v>0.27285</v>
+      </c>
+      <c r="D14">
+        <v>1442.77</v>
+      </c>
+      <c r="E14">
+        <v>0.208</v>
+      </c>
+      <c r="F14">
+        <v>1556.6</v>
+      </c>
+      <c r="G14">
+        <v>0.06485</v>
+      </c>
+      <c r="H14">
+        <v>0.096432</v>
+      </c>
+      <c r="I14">
+        <v>2442.054</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15">
+        <v>0.32379</v>
+      </c>
+      <c r="D15">
+        <v>1378.5</v>
+      </c>
+      <c r="E15">
+        <v>0.25815</v>
+      </c>
+      <c r="F15">
+        <v>1459.94</v>
+      </c>
+      <c r="G15">
+        <v>0.06565</v>
+      </c>
+      <c r="H15">
+        <v>0.111672</v>
+      </c>
+      <c r="I15">
+        <v>2472.432</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16">
+        <v>0.31181</v>
+      </c>
+      <c r="D16">
+        <v>1390.01</v>
+      </c>
+      <c r="E16">
+        <v>0.24359</v>
+      </c>
+      <c r="F16">
+        <v>1490.04</v>
+      </c>
+      <c r="G16">
+        <v>0.06822</v>
+      </c>
+      <c r="H16">
+        <v>0.089381</v>
+      </c>
+      <c r="I16">
+        <v>2424.152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17">
+        <v>0.30117</v>
+      </c>
+      <c r="D17">
+        <v>1407.41</v>
+      </c>
+      <c r="E17">
+        <v>0.23019</v>
+      </c>
+      <c r="F17">
+        <v>1495.44</v>
+      </c>
+      <c r="G17">
+        <v>0.07098</v>
+      </c>
+      <c r="H17">
+        <v>0.142678</v>
+      </c>
+      <c r="I17">
+        <v>2540.252</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18">
+        <v>0.28818</v>
+      </c>
+      <c r="D18">
+        <v>1427.38</v>
+      </c>
+      <c r="E18">
+        <v>0.2203</v>
+      </c>
+      <c r="F18">
+        <v>1515.57</v>
+      </c>
+      <c r="G18">
+        <v>0.06788</v>
+      </c>
+      <c r="H18">
+        <v>0.146058</v>
+      </c>
+      <c r="I18">
+        <v>2557.702</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19">
+        <v>0.27336</v>
+      </c>
+      <c r="D19">
+        <v>1446.07</v>
+      </c>
+      <c r="E19">
+        <v>0.21252</v>
+      </c>
+      <c r="F19">
+        <v>1515.42</v>
+      </c>
+      <c r="G19">
+        <v>0.06084</v>
+      </c>
+      <c r="H19">
+        <v>0.191501</v>
+      </c>
+      <c r="I19">
+        <v>2649.376</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20">
+        <v>0.25815</v>
+      </c>
+      <c r="D20">
+        <v>1459.94</v>
+      </c>
+      <c r="E20">
+        <v>0.20527</v>
+      </c>
+      <c r="F20">
+        <v>1523.66</v>
+      </c>
+      <c r="G20">
+        <v>0.05287</v>
+      </c>
+      <c r="H20">
+        <v>0.19013</v>
+      </c>
+      <c r="I20">
+        <v>2643.634</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
         <v>28</v>
       </c>
-      <c r="C11">
+      <c r="B21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21">
+        <v>0.30526</v>
+      </c>
+      <c r="D21">
+        <v>1420.82</v>
+      </c>
+      <c r="E21">
+        <v>0.26586</v>
+      </c>
+      <c r="F21">
+        <v>1466.86</v>
+      </c>
+      <c r="G21">
+        <v>0.0394</v>
+      </c>
+      <c r="H21">
+        <v>0.135508</v>
+      </c>
+      <c r="I21">
+        <v>2558.582</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22">
+        <v>0.29904</v>
+      </c>
+      <c r="D22">
+        <v>1431.41</v>
+      </c>
+      <c r="E22">
+        <v>0.2541</v>
+      </c>
+      <c r="F22">
+        <v>1471.61</v>
+      </c>
+      <c r="G22">
+        <v>0.04494</v>
+      </c>
+      <c r="H22">
+        <v>0.218789</v>
+      </c>
+      <c r="I22">
+        <v>2710.823</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23">
+        <v>0.29212</v>
+      </c>
+      <c r="D23">
+        <v>1442.32</v>
+      </c>
+      <c r="E23">
+        <v>0.2446</v>
+      </c>
+      <c r="F23">
+        <v>1487.93</v>
+      </c>
+      <c r="G23">
+        <v>0.04752</v>
+      </c>
+      <c r="H23">
+        <v>0.209477</v>
+      </c>
+      <c r="I23">
+        <v>2705.608</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24">
+        <v>0.28446</v>
+      </c>
+      <c r="D24">
+        <v>1431.67</v>
+      </c>
+      <c r="E24">
+        <v>0.23544</v>
+      </c>
+      <c r="F24">
+        <v>1501.69</v>
+      </c>
+      <c r="G24">
+        <v>0.04902</v>
+      </c>
+      <c r="H24">
+        <v>0.11667</v>
+      </c>
+      <c r="I24">
+        <v>2496.68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25">
         <v>0.33146</v>
       </c>
-      <c r="D11">
+      <c r="D25">
         <v>1404.66</v>
       </c>
-      <c r="E11">
+      <c r="E25">
+        <v>0.31333</v>
+      </c>
+      <c r="F25">
+        <v>1412.19</v>
+      </c>
+      <c r="G25">
+        <v>0.01813</v>
+      </c>
+      <c r="H25">
+        <v>0.43426</v>
+      </c>
+      <c r="I25">
+        <v>2941.556</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26">
+        <v>0.32616</v>
+      </c>
+      <c r="D26">
+        <v>1393.56</v>
+      </c>
+      <c r="E26">
+        <v>0.31058</v>
+      </c>
+      <c r="F26">
+        <v>1411.51</v>
+      </c>
+      <c r="G26">
+        <v>0.01558</v>
+      </c>
+      <c r="H26">
+        <v>0.09862899999999999</v>
+      </c>
+      <c r="I26">
+        <v>2478.71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27">
+        <v>0.31866</v>
+      </c>
+      <c r="D27">
+        <v>1410.72</v>
+      </c>
+      <c r="E27">
+        <v>0.30698</v>
+      </c>
+      <c r="F27">
+        <v>1431.45</v>
+      </c>
+      <c r="G27">
+        <v>0.01169</v>
+      </c>
+      <c r="H27">
+        <v>0.009684999999999999</v>
+      </c>
+      <c r="I27">
+        <v>2282.428</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28">
+        <v>0.31333</v>
+      </c>
+      <c r="D28">
+        <v>1412.19</v>
+      </c>
+      <c r="E28">
         <v>0.30331</v>
       </c>
-      <c r="F11">
+      <c r="F28">
         <v>1429.4</v>
       </c>
-      <c r="G11">
-        <v>0.02815</v>
-      </c>
-      <c r="H11">
-        <v>0.175835</v>
-      </c>
-      <c r="I11">
-        <v>2643.931</v>
+      <c r="G28">
+        <v>0.01002</v>
+      </c>
+      <c r="H28">
+        <v>0.020616</v>
+      </c>
+      <c r="I28">
+        <v>2300.137</v>
       </c>
     </row>
   </sheetData>
